--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/IDAHO_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/IDAHO_2019.xlsx
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C154">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C459">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C469">
